--- a/sheets/조재수대금교본/검수/내 나이가 어때서.xlsx
+++ b/sheets/조재수대금교본/검수/내 나이가 어때서.xlsx
@@ -3188,7 +3188,7 @@
       <c r="C3" s="22"/>
       <c r="D3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋∽</t>
+          <t xml:space="preserve">淋</t>
         </is>
       </c>
       <c r="E3" s="22"/>
@@ -3202,14 +3202,14 @@
       <c r="H3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△淋
-湳淋∽</t>
+湳淋</t>
         </is>
       </c>
       <c r="I3" s="22"/>
       <c r="J3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△湳
-–Z</t>
+–</t>
         </is>
       </c>
       <c r="K3" s="22"/>
@@ -3221,8 +3221,7 @@
       <c r="M3" s="22"/>
       <c r="N3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳ㄱ
-∽
+          <t xml:space="preserve">湳
 –</t>
         </is>
       </c>
@@ -3232,19 +3231,13 @@
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z
-湳</t>
+          <t xml:space="preserve">湳</t>
         </is>
       </c>
       <c r="C4" s="23"/>
       <c r="D4" s="21"/>
       <c r="E4" s="23"/>
-      <c r="F4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z
-Z</t>
-        </is>
-      </c>
+      <c r="F4" s="21"/>
       <c r="G4" s="23"/>
       <c r="H4" s="21" t="inlineStr">
         <is>
@@ -3255,8 +3248,7 @@
       <c r="I4" s="23"/>
       <c r="J4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z
-淋</t>
+          <t xml:space="preserve">淋</t>
         </is>
       </c>
       <c r="K4" s="23"/>
@@ -3269,8 +3261,7 @@
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">△∧
-И</t>
+          <t xml:space="preserve">△</t>
         </is>
       </c>
       <c r="C5" s="24"/>
@@ -3283,7 +3274,7 @@
       <c r="F5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△淋
-–Z</t>
+–</t>
         </is>
       </c>
       <c r="G5" s="24"/>
@@ -3296,7 +3287,7 @@
       <c r="J5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△㳞
-–Z</t>
+–</t>
         </is>
       </c>
       <c r="K5" s="24"/>
@@ -3314,15 +3305,11 @@
       <c r="B6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">湳
-淋ʒ</t>
+淋</t>
         </is>
       </c>
       <c r="C6" s="22"/>
-      <c r="D6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D6" s="21"/>
       <c r="E6" s="22"/>
       <c r="F6" s="21" t="inlineStr">
         <is>
@@ -3349,8 +3336,7 @@
       <c r="M6" s="22"/>
       <c r="N6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞
-‹</t>
+          <t xml:space="preserve">㳞</t>
         </is>
       </c>
       <c r="O6" s="22"/>
@@ -3365,7 +3351,7 @@
       <c r="C7" s="23"/>
       <c r="D7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳∧
+          <t xml:space="preserve">湳
 –</t>
         </is>
       </c>
@@ -3373,7 +3359,7 @@
       <c r="F7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△湳
-–∧</t>
+–</t>
         </is>
       </c>
       <c r="G7" s="23"/>
@@ -3386,21 +3372,21 @@
       <c r="I7" s="23"/>
       <c r="J7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋∽</t>
+          <t xml:space="preserve">淋</t>
         </is>
       </c>
       <c r="K7" s="23"/>
       <c r="L7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-潢Z</t>
+潢</t>
         </is>
       </c>
       <c r="M7" s="23"/>
       <c r="N7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋湳
-Z淋</t>
+淋</t>
         </is>
       </c>
       <c r="O7" s="23"/>
@@ -3411,22 +3397,20 @@
       <c r="C8" s="24"/>
       <c r="D8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z
-湳⌝</t>
+          <t xml:space="preserve">湳</t>
         </is>
       </c>
       <c r="E8" s="24"/>
       <c r="F8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">湳
-淋ʒ</t>
+淋</t>
         </is>
       </c>
       <c r="G8" s="24"/>
       <c r="H8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z
-汰</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="I8" s="24"/>
@@ -3465,8 +3449,7 @@
       <c r="G9" s="22"/>
       <c r="H9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">△潢
-И</t>
+          <t xml:space="preserve">△潢</t>
         </is>
       </c>
       <c r="I9" s="22"/>
@@ -3500,9 +3483,7 @@
       <c r="C10" s="23"/>
       <c r="D10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-⌝
-‹</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E10" s="23"/>
@@ -3511,21 +3492,13 @@
       <c r="H10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-林ʒ</t>
+林</t>
         </is>
       </c>
       <c r="I10" s="23"/>
-      <c r="J10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J10" s="21"/>
       <c r="K10" s="23"/>
-      <c r="L10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L10" s="21"/>
       <c r="M10" s="23"/>
       <c r="N10" s="21"/>
       <c r="O10" s="23"/>
@@ -3541,14 +3514,14 @@
       <c r="D11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△㳞
-淋ㄴ</t>
+淋</t>
         </is>
       </c>
       <c r="E11" s="24"/>
       <c r="F11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△湳
-–Z</t>
+–</t>
         </is>
       </c>
       <c r="G11" s="24"/>
@@ -3561,14 +3534,14 @@
       <c r="J11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△湳
-–∧</t>
+–</t>
         </is>
       </c>
       <c r="K11" s="24"/>
       <c r="L11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-㳞Z</t>
+㳞</t>
         </is>
       </c>
       <c r="M11" s="24"/>
@@ -3591,16 +3564,14 @@
       <c r="C12" s="22"/>
       <c r="D12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋⌝
-汰ʒ
-∽</t>
+          <t xml:space="preserve">淋
+汰</t>
         </is>
       </c>
       <c r="E12" s="22"/>
       <c r="F12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Z
-淋</t>
+          <t xml:space="preserve">淋</t>
         </is>
       </c>
       <c r="G12" s="22"/>
@@ -3609,7 +3580,7 @@
       <c r="J12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">湳
-淋∽</t>
+淋</t>
         </is>
       </c>
       <c r="K12" s="22"/>
@@ -3645,7 +3616,7 @@
       <c r="F13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△㳞
-–Z</t>
+–</t>
         </is>
       </c>
       <c r="G13" s="23"/>
@@ -3665,8 +3636,7 @@
       <c r="M13" s="23"/>
       <c r="N13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">△湳
-ZZ</t>
+          <t xml:space="preserve">△湳</t>
         </is>
       </c>
       <c r="O13" s="23"/>
@@ -3679,11 +3649,7 @@
         </is>
       </c>
       <c r="C14" s="24"/>
-      <c r="D14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D14" s="21"/>
       <c r="E14" s="24"/>
       <c r="F14" s="21" t="inlineStr">
         <is>
@@ -3692,17 +3658,9 @@
         </is>
       </c>
       <c r="G14" s="24"/>
-      <c r="H14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H14" s="21"/>
       <c r="I14" s="24"/>
-      <c r="J14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J14" s="21"/>
       <c r="K14" s="24"/>
       <c r="L14" s="21" t="inlineStr">
         <is>
@@ -3714,7 +3672,7 @@
       <c r="N14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋
-湳淋∽</t>
+湳淋</t>
         </is>
       </c>
       <c r="O14" s="24"/>

--- a/sheets/조재수대금교본/검수/내 나이가 어때서.xlsx
+++ b/sheets/조재수대금교본/검수/내 나이가 어때서.xlsx
@@ -3188,7 +3188,7 @@
       <c r="C3" s="22"/>
       <c r="D3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋</t>
+          <t xml:space="preserve">淋∽</t>
         </is>
       </c>
       <c r="E3" s="22"/>
@@ -3202,14 +3202,14 @@
       <c r="H3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△淋
-湳淋</t>
+湳淋∽</t>
         </is>
       </c>
       <c r="I3" s="22"/>
       <c r="J3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△湳
-–</t>
+–Z</t>
         </is>
       </c>
       <c r="K3" s="22"/>
@@ -3221,7 +3221,8 @@
       <c r="M3" s="22"/>
       <c r="N3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳
+          <t xml:space="preserve">湳ㄱ
+∽
 –</t>
         </is>
       </c>
@@ -3231,13 +3232,19 @@
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳</t>
+          <t xml:space="preserve">Z
+湳</t>
         </is>
       </c>
       <c r="C4" s="23"/>
       <c r="D4" s="21"/>
       <c r="E4" s="23"/>
-      <c r="F4" s="21"/>
+      <c r="F4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z
+Z</t>
+        </is>
+      </c>
       <c r="G4" s="23"/>
       <c r="H4" s="21" t="inlineStr">
         <is>
@@ -3248,7 +3255,8 @@
       <c r="I4" s="23"/>
       <c r="J4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋</t>
+          <t xml:space="preserve">Z
+淋</t>
         </is>
       </c>
       <c r="K4" s="23"/>
@@ -3261,7 +3269,8 @@
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">△</t>
+          <t xml:space="preserve">△∧
+И</t>
         </is>
       </c>
       <c r="C5" s="24"/>
@@ -3274,7 +3283,7 @@
       <c r="F5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△淋
-–</t>
+–Z</t>
         </is>
       </c>
       <c r="G5" s="24"/>
@@ -3287,7 +3296,7 @@
       <c r="J5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△㳞
-–</t>
+–Z</t>
         </is>
       </c>
       <c r="K5" s="24"/>
@@ -3305,7 +3314,7 @@
       <c r="B6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">湳
-淋</t>
+淋ʒ</t>
         </is>
       </c>
       <c r="C6" s="22"/>
@@ -3351,7 +3360,7 @@
       <c r="C7" s="23"/>
       <c r="D7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳
+          <t xml:space="preserve">湳∧
 –</t>
         </is>
       </c>
@@ -3359,7 +3368,7 @@
       <c r="F7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△湳
-–</t>
+–∧</t>
         </is>
       </c>
       <c r="G7" s="23"/>
@@ -3372,21 +3381,21 @@
       <c r="I7" s="23"/>
       <c r="J7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋</t>
+          <t xml:space="preserve">淋∽</t>
         </is>
       </c>
       <c r="K7" s="23"/>
       <c r="L7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-潢</t>
+潢Z</t>
         </is>
       </c>
       <c r="M7" s="23"/>
       <c r="N7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋湳
-淋</t>
+Z淋</t>
         </is>
       </c>
       <c r="O7" s="23"/>
@@ -3397,20 +3406,22 @@
       <c r="C8" s="24"/>
       <c r="D8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳</t>
+          <t xml:space="preserve">Z
+湳⌝</t>
         </is>
       </c>
       <c r="E8" s="24"/>
       <c r="F8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">湳
-淋</t>
+淋ʒ</t>
         </is>
       </c>
       <c r="G8" s="24"/>
       <c r="H8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">Z
+汰</t>
         </is>
       </c>
       <c r="I8" s="24"/>
@@ -3449,7 +3460,8 @@
       <c r="G9" s="22"/>
       <c r="H9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">△潢</t>
+          <t xml:space="preserve">△潢
+И</t>
         </is>
       </c>
       <c r="I9" s="22"/>
@@ -3483,7 +3495,8 @@
       <c r="C10" s="23"/>
       <c r="D10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
+          <t xml:space="preserve">–
+⌝</t>
         </is>
       </c>
       <c r="E10" s="23"/>
@@ -3492,7 +3505,7 @@
       <c r="H10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-林</t>
+林ʒ</t>
         </is>
       </c>
       <c r="I10" s="23"/>
@@ -3514,14 +3527,14 @@
       <c r="D11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△㳞
-淋</t>
+淋ㄴ</t>
         </is>
       </c>
       <c r="E11" s="24"/>
       <c r="F11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△湳
-–</t>
+–Z</t>
         </is>
       </c>
       <c r="G11" s="24"/>
@@ -3534,14 +3547,14 @@
       <c r="J11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△湳
-–</t>
+–∧</t>
         </is>
       </c>
       <c r="K11" s="24"/>
       <c r="L11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-㳞</t>
+㳞Z</t>
         </is>
       </c>
       <c r="M11" s="24"/>
@@ -3564,14 +3577,16 @@
       <c r="C12" s="22"/>
       <c r="D12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋
-汰</t>
+          <t xml:space="preserve">淋⌝
+汰ʒ
+∽</t>
         </is>
       </c>
       <c r="E12" s="22"/>
       <c r="F12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋</t>
+          <t xml:space="preserve">Z
+淋</t>
         </is>
       </c>
       <c r="G12" s="22"/>
@@ -3580,7 +3595,7 @@
       <c r="J12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">湳
-淋</t>
+淋∽</t>
         </is>
       </c>
       <c r="K12" s="22"/>
@@ -3616,7 +3631,7 @@
       <c r="F13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△㳞
-–</t>
+–Z</t>
         </is>
       </c>
       <c r="G13" s="23"/>
@@ -3636,7 +3651,8 @@
       <c r="M13" s="23"/>
       <c r="N13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">△湳</t>
+          <t xml:space="preserve">△湳
+ZZ</t>
         </is>
       </c>
       <c r="O13" s="23"/>
@@ -3672,7 +3688,7 @@
       <c r="N14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋
-湳淋</t>
+湳淋∽</t>
         </is>
       </c>
       <c r="O14" s="24"/>

--- a/sheets/조재수대금교본/검수/내 나이가 어때서.xlsx
+++ b/sheets/조재수대금교본/검수/내 나이가 어때서.xlsx
@@ -3137,26 +3137,26 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="13.46" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="13.46" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="13.46" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="13.46" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="13.46" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="13.46" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="13.46" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="64.52" customHeight="true">
+    <row r="2" ht="65.57" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
       <c r="N2" s="20"/>
       <c r="O2" s="20"/>
     </row>
-    <row r="3" ht="96.05" customHeight="true">
+    <row r="3" ht="97.63" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -3228,7 +3228,7 @@
       </c>
       <c r="O3" s="22"/>
     </row>
-    <row r="4" ht="96.05" customHeight="true">
+    <row r="4" ht="97.63" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -3265,7 +3265,7 @@
       <c r="N4" s="21"/>
       <c r="O4" s="23"/>
     </row>
-    <row r="5" ht="96.05" customHeight="true">
+    <row r="5" ht="97.63" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -3309,7 +3309,7 @@
       </c>
       <c r="O5" s="24"/>
     </row>
-    <row r="6" ht="96.05" customHeight="true">
+    <row r="6" ht="97.63" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -3350,7 +3350,7 @@
       </c>
       <c r="O6" s="22"/>
     </row>
-    <row r="7" ht="96.05" customHeight="true">
+    <row r="7" ht="97.63" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -3400,7 +3400,7 @@
       </c>
       <c r="O7" s="23"/>
     </row>
-    <row r="8" ht="96.05" customHeight="true">
+    <row r="8" ht="97.63" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21"/>
       <c r="C8" s="24"/>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="O8" s="24"/>
     </row>
-    <row r="9" ht="96.05" customHeight="true">
+    <row r="9" ht="97.63" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21"/>
       <c r="C9" s="22"/>
@@ -3484,7 +3484,7 @@
       </c>
       <c r="O9" s="22"/>
     </row>
-    <row r="10" ht="96.05" customHeight="true">
+    <row r="10" ht="97.63" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -3516,7 +3516,7 @@
       <c r="N10" s="21"/>
       <c r="O10" s="23"/>
     </row>
-    <row r="11" ht="96.05" customHeight="true">
+    <row r="11" ht="97.63" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -3566,7 +3566,7 @@
       </c>
       <c r="O11" s="24"/>
     </row>
-    <row r="12" ht="96.05" customHeight="true">
+    <row r="12" ht="97.63" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="O12" s="22"/>
     </row>
-    <row r="13" ht="96.05" customHeight="true">
+    <row r="13" ht="97.63" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -3657,7 +3657,7 @@
       </c>
       <c r="O13" s="23"/>
     </row>
-    <row r="14" ht="96.05" customHeight="true">
+    <row r="14" ht="97.63" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -3699,6 +3699,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="62"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="61"/>
 </worksheet>
 </file>